--- a/humaniseT5/_tests/fake_authored_data_cases.xlsx
+++ b/humaniseT5/_tests/fake_authored_data_cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Python\Sophont\humaniseT5\_tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F00F4E-038B-43E6-BA2D-A6A3241577BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B865245E-1031-4A54-B945-41C3A632F346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17640" yWindow="1080" windowWidth="15720" windowHeight="19545" xr2:uid="{53B79B23-3148-4916-AC13-D951DB90D9AE}"/>
+    <workbookView xWindow="6645" yWindow="1230" windowWidth="24270" windowHeight="19695" xr2:uid="{53B79B23-3148-4916-AC13-D951DB90D9AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>single int</t>
   </si>
@@ -108,6 +108,9 @@
 *Dragging*. A character can drag a load of 20x Strength 
 for under one minute.
 ```</t>
+  </si>
+  <si>
+    <t>empty</t>
   </si>
 </sst>
 </file>
@@ -482,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D734887-B0ED-45B9-A93E-DE446302856E}">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -493,10 +496,11 @@
     <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.7109375" customWidth="1"/>
+    <col min="10" max="10" width="37.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -522,10 +526,13 @@
         <v>12</v>
       </c>
       <c r="I1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>57</v>
       </c>
@@ -550,7 +557,7 @@
       <c r="H2" t="b">
         <v>0</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>14</v>
       </c>
     </row>
